--- a/КартаMB.xlsx
+++ b/КартаMB.xlsx
@@ -13,11 +13,9 @@
   </bookViews>
   <sheets>
     <sheet name="DI_Status" sheetId="2" r:id="rId1"/>
-    <sheet name="DI_Config" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DI_Config!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DI_Status!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DI_Status!$A$1:$N$3</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>№</t>
   </si>
@@ -79,43 +77,22 @@
     <t>непосредственно</t>
   </si>
   <si>
-    <t>Holding Registers</t>
-  </si>
-  <si>
     <t>RW</t>
   </si>
   <si>
-    <t>RO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQ1 Дверца станции открыта </t>
-  </si>
-  <si>
-    <t>SA1.1 ШУМП. Управление с пультов</t>
-  </si>
-  <si>
-    <t>SA1.2 ШУМП. Управление со шкафа</t>
-  </si>
-  <si>
-    <t>DI_001_Status</t>
-  </si>
-  <si>
     <t>Input Registers</t>
   </si>
   <si>
-    <t>DI_002_Status</t>
-  </si>
-  <si>
-    <t>DI_003_Status</t>
-  </si>
-  <si>
-    <t>DI_001_Config</t>
-  </si>
-  <si>
-    <t>DI_002_Config</t>
-  </si>
-  <si>
-    <t>DI_003_Config</t>
+    <t>JTH_Temper</t>
+  </si>
+  <si>
+    <t>Температура</t>
+  </si>
+  <si>
+    <t>JTH_humidity</t>
+  </si>
+  <si>
+    <t>Влажность</t>
   </si>
 </sst>
 </file>
@@ -463,7 +440,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист5"/>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" customWidth="1"/>
@@ -477,7 +454,7 @@
     <col min="9" max="9" width="11.88671875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="66.599999999999994" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
@@ -535,16 +512,16 @@
         <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>101</v>
+        <v>768</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -552,7 +529,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -561,191 +538,20 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>103</v>
+        <v>769</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>105</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Лист7"/>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="4.88671875" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" customWidth="1"/>
-    <col min="4" max="4" width="2.44140625" customWidth="1"/>
-    <col min="5" max="5" width="3.77734375" customWidth="1"/>
-    <col min="6" max="6" width="7.109375" customWidth="1"/>
-    <col min="7" max="7" width="3.44140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="42.88671875" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="66.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2">
-        <v>101</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3">
-        <v>103</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4">
-        <v>105</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>